--- a/excels/Horarios ICIF 202620 Enviado 3.xlsx
+++ b/excels/Horarios ICIF 202620 Enviado 3.xlsx
@@ -8,25 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACAEA7D-EA86-4CE2-996D-D38C835E4736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAAEF1-C37C-4B47-BCCF-3F4F84225683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Semestre 2" sheetId="5" r:id="rId1"/>
-    <sheet name="Semestre 3" sheetId="4" r:id="rId2"/>
-    <sheet name="Semestre 4" sheetId="2" r:id="rId3"/>
-    <sheet name="Semestre 6_nueva" sheetId="6" r:id="rId4"/>
-    <sheet name="Semestre 6_antigua" sheetId="7" r:id="rId5"/>
-    <sheet name="Semestre 8" sheetId="3" r:id="rId6"/>
-    <sheet name="Semestre 10" sheetId="8" r:id="rId7"/>
+    <sheet name="Semestre 1" sheetId="9" r:id="rId1"/>
+    <sheet name="Semestre 2" sheetId="5" r:id="rId2"/>
+    <sheet name="Semestre 3" sheetId="4" r:id="rId3"/>
+    <sheet name="Semestre 4" sheetId="2" r:id="rId4"/>
+    <sheet name="Semestre 6_nueva" sheetId="6" r:id="rId5"/>
+    <sheet name="Semestre 6_antigua" sheetId="7" r:id="rId6"/>
+    <sheet name="Semestre 8" sheetId="3" r:id="rId7"/>
+    <sheet name="Semestre 10" sheetId="8" r:id="rId8"/>
+    <sheet name="Ingleses" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="368">
   <si>
     <t>NRC</t>
   </si>
@@ -1037,6 +1039,99 @@
   </si>
   <si>
     <t>13914</t>
+  </si>
+  <si>
+    <t>12073</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>ALGEBRA</t>
+  </si>
+  <si>
+    <t>ICOM</t>
+  </si>
+  <si>
+    <t>12077</t>
+  </si>
+  <si>
+    <t>4282</t>
+  </si>
+  <si>
+    <t>0007</t>
+  </si>
+  <si>
+    <t>4284</t>
+  </si>
+  <si>
+    <t>5368</t>
+  </si>
+  <si>
+    <t>8442</t>
+  </si>
+  <si>
+    <t>0008</t>
+  </si>
+  <si>
+    <t>INTRODUCCION AL CALCULO</t>
+  </si>
+  <si>
+    <t>REYES/MONSALVE</t>
+  </si>
+  <si>
+    <t>ICMI</t>
+  </si>
+  <si>
+    <t>8443</t>
+  </si>
+  <si>
+    <t>ICIV</t>
+  </si>
+  <si>
+    <t>4281</t>
+  </si>
+  <si>
+    <t>5366</t>
+  </si>
+  <si>
+    <t>5367</t>
+  </si>
+  <si>
+    <t>8441</t>
+  </si>
+  <si>
+    <t>5777</t>
+  </si>
+  <si>
+    <t>1416</t>
+  </si>
+  <si>
+    <t>INGLES II</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>ESCOBAR/AGURTO</t>
+  </si>
+  <si>
+    <t>5875</t>
+  </si>
+  <si>
+    <t>1431</t>
+  </si>
+  <si>
+    <t>INGLES TECNICO</t>
+  </si>
+  <si>
+    <t>5876</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
+  </si>
+  <si>
+    <t>BENAVENTE/ULLOA</t>
   </si>
 </sst>
 </file>
@@ -1464,6 +1559,1318 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33AB8C9A-831E-4FA0-B6F6-A0D2666A1987}">
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" s="2"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S5" s="2"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S6" s="2"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S8" s="2"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S9" s="2"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="S12" s="2"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="S16" s="1"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="S17" s="1"/>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="S18" s="1"/>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S19" s="1"/>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="S21" s="1"/>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="S25" s="1"/>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="S26" s="1"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="S27" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B04450B-4D3A-444A-8C70-833821F0E18C}">
   <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -3045,7 +4452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742B1EB3-54E8-42B1-96A5-AD861CB086AD}">
   <dimension ref="A1:S31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -4526,7 +5933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31639A8-B77F-40D3-A3E2-D8298BF83C8B}">
   <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -5965,7 +7372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BD2444-5417-4C3B-ACAC-17D64029070C}">
   <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -7453,7 +8860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8ABF100-BEC0-4DD6-AD50-C4B8A3F777CB}">
   <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -9576,7 +10983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE4429E-CA1B-4529-94AE-CE97ED6F115A}">
   <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -10937,7 +12344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E82A5-8A64-4B2B-8701-1D6FF57E175E}">
   <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
@@ -11723,4 +13130,384 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8554B521-5B20-4750-BD74-44BFF8934136}">
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="7" max="7" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/excels/Horarios ICIF 202620 Enviado 3.xlsx
+++ b/excels/Horarios ICIF 202620 Enviado 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAAEF1-C37C-4B47-BCCF-3F4F84225683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B12831-7E1D-42CE-B302-B5809EF04DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semestre 1" sheetId="9" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="370">
   <si>
     <t>NRC</t>
   </si>
@@ -1132,6 +1132,12 @@
   </si>
   <si>
     <t>BENAVENTE/ULLOA</t>
+  </si>
+  <si>
+    <t>21668</t>
+  </si>
+  <si>
+    <t>21670</t>
   </si>
 </sst>
 </file>
@@ -7374,7 +7380,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BD2444-5417-4C3B-ACAC-17D64029070C}">
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="7" max="7" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -8449,411 +8455,943 @@
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="S25" s="6"/>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="S26" s="6"/>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="S27" s="6"/>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="S28" s="6"/>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1" t="s">
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1" t="s">
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R25" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S25" s="1"/>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="A26" s="1" t="s">
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1" t="s">
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R26" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S26" s="1"/>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="A27" s="1" t="s">
+      <c r="S30" s="1"/>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="B31" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1" t="s">
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1" t="s">
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="R27" s="1" t="s">
+      <c r="R31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="S27" s="1"/>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="A28" s="1" t="s">
+      <c r="S31" s="1"/>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G32" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1" t="s">
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="R32" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="S28" s="1"/>
-    </row>
-    <row r="29" spans="1:19">
-      <c r="A29" s="6" t="s">
+      <c r="S32" s="1"/>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B33" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D33" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G33" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I33" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J33" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6" t="s">
+      <c r="K33" s="6"/>
+      <c r="L33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6" t="s">
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R29" s="6" t="s">
+      <c r="R33" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="S29" s="6"/>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="6" t="s">
+      <c r="S33" s="6"/>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C30" s="6" t="s">
+      <c r="B34" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D34" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E34" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F34" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I34" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6" t="s">
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R30" s="6" t="s">
+      <c r="R34" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="S30" s="6"/>
-    </row>
-    <row r="31" spans="1:19">
-      <c r="A31" s="6" t="s">
+      <c r="S34" s="6"/>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C31" s="6" t="s">
+      <c r="B35" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D35" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F35" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J35" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6" t="s">
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6" t="s">
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R31" s="6" t="s">
+      <c r="R35" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="S31" s="6"/>
-    </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="6" t="s">
+      <c r="S35" s="6"/>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="B36" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D36" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E36" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F36" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H36" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I36" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K36" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6" t="s">
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="R32" s="6" t="s">
+      <c r="R36" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="S32" s="6"/>
-    </row>
-    <row r="33" spans="1:19">
-      <c r="A33" s="4" t="s">
+      <c r="S36" s="6"/>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="B37" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4" t="s">
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="R33" s="4" t="s">
+      <c r="R37" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="S33" s="4"/>
+      <c r="S37" s="4"/>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="S38" s="3"/>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M39" s="3"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="1:19">
+      <c r="A42" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="1:19">
+      <c r="A43" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="A44" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="A45" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="S45" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excels/Horarios ICIF 202620 Enviado 3.xlsx
+++ b/excels/Horarios ICIF 202620 Enviado 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B12831-7E1D-42CE-B302-B5809EF04DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC25341-B320-4B88-AF48-6FE23D4CDCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semestre 1" sheetId="9" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="377">
   <si>
     <t>NRC</t>
   </si>
@@ -1138,6 +1138,27 @@
   </si>
   <si>
     <t>21670</t>
+  </si>
+  <si>
+    <t>13757</t>
+  </si>
+  <si>
+    <t>13758</t>
+  </si>
+  <si>
+    <t>T1G</t>
+  </si>
+  <si>
+    <t>13759</t>
+  </si>
+  <si>
+    <t>T1H</t>
+  </si>
+  <si>
+    <t>13760</t>
+  </si>
+  <si>
+    <t>T1I</t>
   </si>
 </sst>
 </file>
@@ -2878,7 +2899,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B04450B-4D3A-444A-8C70-833821F0E18C}">
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -4452,6 +4473,382 @@
         <v>86</v>
       </c>
       <c r="S33" s="1"/>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S34" s="2"/>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S35" s="2"/>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S36" s="2"/>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="S37" s="2"/>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S39" s="2"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S40" s="2"/>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excels/Horarios ICIF 202620 Enviado 3.xlsx
+++ b/excels/Horarios ICIF 202620 Enviado 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benja\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC25341-B320-4B88-AF48-6FE23D4CDCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4414BE8E-0C37-42AD-9723-2F945E2AAE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Semestre 1" sheetId="9" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="372">
   <si>
     <t>NRC</t>
   </si>
@@ -393,9 +393,6 @@
     <t>CORREA/VILLA</t>
   </si>
   <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
     <t>T05</t>
   </si>
   <si>
@@ -681,22 +678,10 @@
     <t>JOSE</t>
   </si>
   <si>
-    <t>21463</t>
-  </si>
-  <si>
     <t>MATEMATICA DISCRETA</t>
   </si>
   <si>
-    <t>CHICATA/CASTRO</t>
-  </si>
-  <si>
-    <t>21467</t>
-  </si>
-  <si>
     <t>RETAMAL/PENA</t>
-  </si>
-  <si>
-    <t>21468</t>
   </si>
   <si>
     <t>21666</t>
@@ -1654,16 +1639,16 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>27</v>
@@ -1672,7 +1657,7 @@
         <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>23</v>
@@ -1701,16 +1686,16 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>27</v>
@@ -1719,7 +1704,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>23</v>
@@ -1745,21 +1730,21 @@
         <v>86</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>32</v>
@@ -1768,7 +1753,7 @@
         <v>21</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>23</v>
@@ -1797,16 +1782,16 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>32</v>
@@ -1815,7 +1800,7 @@
         <v>21</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>23</v>
@@ -1844,16 +1829,16 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>20</v>
@@ -1862,7 +1847,7 @@
         <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>23</v>
@@ -1885,22 +1870,22 @@
         <v>102</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S6" s="2"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>20</v>
@@ -1909,7 +1894,7 @@
         <v>21</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>23</v>
@@ -1932,22 +1917,22 @@
         <v>102</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>27</v>
@@ -1956,7 +1941,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>23</v>
@@ -1979,22 +1964,22 @@
         <v>102</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>27</v>
@@ -2003,7 +1988,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>23</v>
@@ -2026,22 +2011,22 @@
         <v>102</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S9" s="2"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>20</v>
@@ -2050,7 +2035,7 @@
         <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>23</v>
@@ -2079,16 +2064,16 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>20</v>
@@ -2097,7 +2082,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>23</v>
@@ -2123,21 +2108,21 @@
         <v>88</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
@@ -2146,7 +2131,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>23</v>
@@ -2169,22 +2154,22 @@
         <v>85</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S12" s="2"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>20</v>
@@ -2193,7 +2178,7 @@
         <v>21</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>23</v>
@@ -2216,24 +2201,24 @@
         <v>85</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>27</v>
@@ -2242,7 +2227,7 @@
         <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>23</v>
@@ -2265,24 +2250,24 @@
         <v>85</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>27</v>
@@ -2291,7 +2276,7 @@
         <v>21</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>23</v>
@@ -2314,24 +2299,24 @@
         <v>85</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -2340,7 +2325,7 @@
         <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>24</v>
@@ -2363,22 +2348,22 @@
         <v>85</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>42</v>
@@ -2387,7 +2372,7 @@
         <v>43</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>24</v>
@@ -2410,22 +2395,22 @@
         <v>85</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S17" s="1"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -2434,7 +2419,7 @@
         <v>43</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>24</v>
@@ -2457,22 +2442,22 @@
         <v>85</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S18" s="1"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>42</v>
@@ -2481,7 +2466,7 @@
         <v>43</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>24</v>
@@ -2510,16 +2495,16 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>42</v>
@@ -2528,7 +2513,7 @@
         <v>43</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>24</v>
@@ -2554,21 +2539,21 @@
         <v>88</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>42</v>
@@ -2577,7 +2562,7 @@
         <v>43</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>24</v>
@@ -2606,16 +2591,16 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>47</v>
@@ -2624,7 +2609,7 @@
         <v>43</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>24</v>
@@ -2650,21 +2635,21 @@
         <v>86</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>47</v>
@@ -2673,7 +2658,7 @@
         <v>43</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>24</v>
@@ -2699,21 +2684,21 @@
         <v>86</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>47</v>
@@ -2722,7 +2707,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>24</v>
@@ -2748,21 +2733,21 @@
         <v>86</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>42</v>
@@ -2771,7 +2756,7 @@
         <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>24</v>
@@ -2794,22 +2779,22 @@
         <v>85</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>42</v>
@@ -2818,7 +2803,7 @@
         <v>43</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>24</v>
@@ -2841,22 +2826,22 @@
         <v>85</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>42</v>
@@ -2865,7 +2850,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>24</v>
@@ -2888,7 +2873,7 @@
         <v>85</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="S27" s="1"/>
     </row>
@@ -2970,10 +2955,10 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>76</v>
@@ -3004,10 +2989,10 @@
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R2" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S2" s="6" t="s">
         <v>96</v>
@@ -3015,10 +3000,10 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>76</v>
@@ -3049,10 +3034,10 @@
       </c>
       <c r="P3" s="6"/>
       <c r="Q3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S3" s="6" t="s">
         <v>96</v>
@@ -3060,10 +3045,10 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>76</v>
@@ -3094,10 +3079,10 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R4" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S4" s="6" t="s">
         <v>96</v>
@@ -3105,10 +3090,10 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>76</v>
@@ -3139,10 +3124,10 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R5" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S5" s="6" t="s">
         <v>96</v>
@@ -3150,10 +3135,10 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>76</v>
@@ -3184,10 +3169,10 @@
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S6" s="6" t="s">
         <v>96</v>
@@ -3195,10 +3180,10 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>76</v>
@@ -3229,10 +3214,10 @@
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>96</v>
@@ -3240,16 +3225,16 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>42</v>
@@ -3258,7 +3243,7 @@
         <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>24</v>
@@ -3281,7 +3266,7 @@
         <v>85</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>96</v>
@@ -3289,16 +3274,16 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>42</v>
@@ -3307,7 +3292,7 @@
         <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>24</v>
@@ -3330,7 +3315,7 @@
         <v>85</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>96</v>
@@ -3338,16 +3323,16 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>42</v>
@@ -3356,7 +3341,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>24</v>
@@ -3379,7 +3364,7 @@
         <v>85</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>96</v>
@@ -3387,16 +3372,16 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -3405,7 +3390,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>24</v>
@@ -3425,10 +3410,10 @@
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>96</v>
@@ -3436,16 +3421,16 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>47</v>
@@ -3454,7 +3439,7 @@
         <v>43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>24</v>
@@ -3474,10 +3459,10 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>96</v>
@@ -3485,16 +3470,16 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>47</v>
@@ -3503,7 +3488,7 @@
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>24</v>
@@ -3523,10 +3508,10 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>96</v>
@@ -3534,16 +3519,16 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>20</v>
@@ -3552,7 +3537,7 @@
         <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>23</v>
@@ -3575,7 +3560,7 @@
         <v>85</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S14" s="2" t="s">
         <v>96</v>
@@ -3583,16 +3568,16 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>27</v>
@@ -3601,7 +3586,7 @@
         <v>21</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>23</v>
@@ -3621,10 +3606,10 @@
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="S15" s="2" t="s">
         <v>96</v>
@@ -3632,16 +3617,16 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>32</v>
@@ -3650,7 +3635,7 @@
         <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>23</v>
@@ -3670,10 +3655,10 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="S16" s="2" t="s">
         <v>96</v>
@@ -3681,16 +3666,16 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>39</v>
@@ -3699,7 +3684,7 @@
         <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>23</v>
@@ -3719,10 +3704,10 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="S17" s="2" t="s">
         <v>96</v>
@@ -3730,16 +3715,16 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>42</v>
@@ -3748,7 +3733,7 @@
         <v>43</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>24</v>
@@ -3777,16 +3762,16 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>42</v>
@@ -3795,7 +3780,7 @@
         <v>43</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>24</v>
@@ -3824,16 +3809,16 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>42</v>
@@ -3842,7 +3827,7 @@
         <v>43</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>24</v>
@@ -3871,16 +3856,16 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>27</v>
@@ -3889,7 +3874,7 @@
         <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>23</v>
@@ -3918,16 +3903,16 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>47</v>
@@ -3936,7 +3921,7 @@
         <v>43</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>24</v>
@@ -3959,22 +3944,22 @@
         <v>102</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S22" s="1"/>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>47</v>
@@ -3983,7 +3968,7 @@
         <v>43</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>24</v>
@@ -4006,22 +3991,22 @@
         <v>102</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S23" s="1"/>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>47</v>
@@ -4030,7 +4015,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>24</v>
@@ -4053,22 +4038,22 @@
         <v>102</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>39</v>
@@ -4077,7 +4062,7 @@
         <v>21</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>23</v>
@@ -4100,16 +4085,16 @@
         <v>102</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S25" s="2"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>108</v>
@@ -4124,7 +4109,7 @@
         <v>43</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -4149,10 +4134,10 @@
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>108</v>
@@ -4167,7 +4152,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -4194,16 +4179,16 @@
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>63</v>
@@ -4212,7 +4197,7 @@
         <v>43</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>34</v>
@@ -4241,16 +4226,16 @@
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>63</v>
@@ -4259,7 +4244,7 @@
         <v>43</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>34</v>
@@ -4288,16 +4273,16 @@
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>63</v>
@@ -4306,7 +4291,7 @@
         <v>43</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>34</v>
@@ -4335,25 +4320,25 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>34</v>
@@ -4382,25 +4367,25 @@
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>34</v>
@@ -4429,25 +4414,25 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>43</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>34</v>
@@ -4476,16 +4461,16 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>40</v>
@@ -4494,7 +4479,7 @@
         <v>21</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>33</v>
@@ -4523,16 +4508,16 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>40</v>
@@ -4541,7 +4526,7 @@
         <v>21</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>33</v>
@@ -4570,25 +4555,25 @@
     </row>
     <row r="36" spans="1:19">
       <c r="A36" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>33</v>
@@ -4611,31 +4596,31 @@
         <v>102</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S36" s="2"/>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>33</v>
@@ -4658,31 +4643,31 @@
         <v>102</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="S37" s="2"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>33</v>
@@ -4711,25 +4696,25 @@
     </row>
     <row r="39" spans="1:19">
       <c r="A39" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>33</v>
@@ -4758,25 +4743,25 @@
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>33</v>
@@ -4805,25 +4790,25 @@
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>33</v>
@@ -4930,7 +4915,7 @@
         <v>24516</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -4945,7 +4930,7 @@
         <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
@@ -4968,7 +4953,7 @@
         <v>85</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="S2" s="1"/>
     </row>
@@ -4977,7 +4962,7 @@
         <v>24516</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -4992,7 +4977,7 @@
         <v>43</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>24</v>
@@ -5015,7 +5000,7 @@
         <v>85</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="S3" s="1"/>
     </row>
@@ -5024,7 +5009,7 @@
         <v>24516</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -5039,7 +5024,7 @@
         <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>24</v>
@@ -5062,7 +5047,7 @@
         <v>85</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="S4" s="1"/>
     </row>
@@ -5071,7 +5056,7 @@
         <v>24519</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -5086,7 +5071,7 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>24</v>
@@ -5118,7 +5103,7 @@
         <v>24519</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -5133,7 +5118,7 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>24</v>
@@ -5165,7 +5150,7 @@
         <v>24519</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
@@ -5180,7 +5165,7 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>24</v>
@@ -5212,7 +5197,7 @@
         <v>24523</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>18</v>
@@ -5227,7 +5212,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>23</v>
@@ -5259,7 +5244,7 @@
         <v>24524</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
@@ -5274,7 +5259,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>23</v>
@@ -5306,7 +5291,7 @@
         <v>24525</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>18</v>
@@ -5321,7 +5306,7 @@
         <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>23</v>
@@ -5353,7 +5338,7 @@
         <v>24526</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>18</v>
@@ -5368,7 +5353,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>23</v>
@@ -5397,10 +5382,10 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>108</v>
@@ -5409,7 +5394,7 @@
         <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>43</v>
@@ -5434,7 +5419,7 @@
         <v>110</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>96</v>
@@ -5442,10 +5427,10 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>108</v>
@@ -5454,7 +5439,7 @@
         <v>19</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>43</v>
@@ -5479,7 +5464,7 @@
         <v>110</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>96</v>
@@ -5490,7 +5475,7 @@
         <v>24555</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>18</v>
@@ -5505,7 +5490,7 @@
         <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>81</v>
@@ -5528,7 +5513,7 @@
         <v>102</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S14" s="6"/>
     </row>
@@ -5537,7 +5522,7 @@
         <v>24555</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>18</v>
@@ -5552,7 +5537,7 @@
         <v>49</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>81</v>
@@ -5575,7 +5560,7 @@
         <v>102</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S15" s="6"/>
     </row>
@@ -5584,7 +5569,7 @@
         <v>24556</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>18</v>
@@ -5599,7 +5584,7 @@
         <v>49</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>81</v>
@@ -5622,7 +5607,7 @@
         <v>102</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S16" s="6"/>
     </row>
@@ -5631,7 +5616,7 @@
         <v>24556</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>18</v>
@@ -5646,7 +5631,7 @@
         <v>49</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>81</v>
@@ -5669,7 +5654,7 @@
         <v>102</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S17" s="6"/>
     </row>
@@ -5678,7 +5663,7 @@
         <v>24557</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>18</v>
@@ -5693,7 +5678,7 @@
         <v>49</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>44</v>
@@ -5716,7 +5701,7 @@
         <v>102</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S18" s="6"/>
     </row>
@@ -5725,7 +5710,7 @@
         <v>24557</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>18</v>
@@ -5740,7 +5725,7 @@
         <v>49</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>44</v>
@@ -5763,7 +5748,7 @@
         <v>102</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S19" s="6"/>
     </row>
@@ -5772,7 +5757,7 @@
         <v>24559</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>18</v>
@@ -5787,7 +5772,7 @@
         <v>49</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>44</v>
@@ -5810,7 +5795,7 @@
         <v>102</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S20" s="6"/>
     </row>
@@ -5819,7 +5804,7 @@
         <v>24559</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>18</v>
@@ -5834,7 +5819,7 @@
         <v>49</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>44</v>
@@ -5857,22 +5842,22 @@
         <v>102</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S21" s="6"/>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>48</v>
@@ -5881,7 +5866,7 @@
         <v>49</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>44</v>
@@ -5904,22 +5889,22 @@
         <v>102</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S22" s="6"/>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>48</v>
@@ -5928,7 +5913,7 @@
         <v>49</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>44</v>
@@ -5951,22 +5936,22 @@
         <v>102</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S23" s="6"/>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>42</v>
@@ -5975,7 +5960,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>24</v>
@@ -5995,25 +5980,25 @@
       </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>42</v>
@@ -6022,7 +6007,7 @@
         <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>24</v>
@@ -6042,25 +6027,25 @@
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>42</v>
@@ -6069,7 +6054,7 @@
         <v>43</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>24</v>
@@ -6089,25 +6074,25 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>47</v>
@@ -6116,7 +6101,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>34</v>
@@ -6136,25 +6121,25 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>47</v>
@@ -6163,7 +6148,7 @@
         <v>43</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>34</v>
@@ -6183,25 +6168,25 @@
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="S28" s="1"/>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>47</v>
@@ -6210,7 +6195,7 @@
         <v>43</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>34</v>
@@ -6230,25 +6215,25 @@
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="S29" s="1"/>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>51</v>
@@ -6257,7 +6242,7 @@
         <v>49</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>44</v>
@@ -6280,22 +6265,22 @@
         <v>102</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S30" s="6"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>51</v>
@@ -6304,7 +6289,7 @@
         <v>49</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>44</v>
@@ -6327,7 +6312,7 @@
         <v>102</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S31" s="6"/>
     </row>
@@ -6412,7 +6397,7 @@
         <v>97</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>18</v>
@@ -6461,7 +6446,7 @@
         <v>97</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>18</v>
@@ -6507,10 +6492,10 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -6545,19 +6530,19 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -6592,10 +6577,10 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>96</v>
@@ -6603,16 +6588,16 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>42</v>
@@ -6621,7 +6606,7 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>24</v>
@@ -6641,25 +6626,25 @@
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>42</v>
@@ -6668,7 +6653,7 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>24</v>
@@ -6688,25 +6673,25 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>42</v>
@@ -6715,7 +6700,7 @@
         <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>24</v>
@@ -6735,25 +6720,25 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>47</v>
@@ -6762,7 +6747,7 @@
         <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>24</v>
@@ -6793,16 +6778,16 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>47</v>
@@ -6811,7 +6796,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>24</v>
@@ -6840,16 +6825,16 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>47</v>
@@ -6858,7 +6843,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>24</v>
@@ -6889,16 +6874,16 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>52</v>
@@ -6907,7 +6892,7 @@
         <v>49</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>44</v>
@@ -6930,7 +6915,7 @@
         <v>102</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>96</v>
@@ -6938,16 +6923,16 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>52</v>
@@ -6956,7 +6941,7 @@
         <v>49</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>44</v>
@@ -6979,7 +6964,7 @@
         <v>102</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>96</v>
@@ -6987,16 +6972,16 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>53</v>
@@ -7005,7 +6990,7 @@
         <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>44</v>
@@ -7028,7 +7013,7 @@
         <v>102</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>96</v>
@@ -7036,16 +7021,16 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>53</v>
@@ -7054,7 +7039,7 @@
         <v>49</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>44</v>
@@ -7077,7 +7062,7 @@
         <v>102</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>96</v>
@@ -7085,16 +7070,16 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>32</v>
@@ -7103,7 +7088,7 @@
         <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -7119,25 +7104,25 @@
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="S16" s="2"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>32</v>
@@ -7146,7 +7131,7 @@
         <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -7162,25 +7147,25 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>39</v>
@@ -7189,7 +7174,7 @@
         <v>21</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -7205,10 +7190,10 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="R18" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="S18" s="2" t="s">
         <v>80</v>
@@ -7216,16 +7201,16 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>39</v>
@@ -7234,7 +7219,7 @@
         <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -7250,10 +7235,10 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>80</v>
@@ -7261,16 +7246,16 @@
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>40</v>
@@ -7279,7 +7264,7 @@
         <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -7298,22 +7283,22 @@
         <v>101</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S20" s="2"/>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>40</v>
@@ -7322,7 +7307,7 @@
         <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -7341,257 +7326,259 @@
         <v>101</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S21" s="2"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="A22" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="D22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="S22" s="2"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1" t="s">
+      <c r="G23" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="S22" s="1"/>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="S23" s="2"/>
-    </row>
-    <row r="24" spans="1:19">
-      <c r="A24" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="S24" s="2"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="2" t="s">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>145</v>
+        <v>319</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>27</v>
+        <v>322</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="M25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="1">
+        <v>21463</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1610</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="R25" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="S25" s="2"/>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="A26" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="R26" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="S26" s="2"/>
+      <c r="R26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="2" t="s">
-        <v>242</v>
+      <c r="A27" s="2">
+        <v>21467</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>20</v>
@@ -7600,157 +7587,157 @@
         <v>21</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1610</v>
+      </c>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2" t="s">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="S27" s="2"/>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="S28" s="1" t="s">
+      <c r="A28" s="2">
+        <v>21467</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="D28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1440</v>
+      </c>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="S28" s="2"/>
     </row>
     <row r="29" spans="1:19">
-      <c r="A29" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1" t="s">
+      <c r="A29" s="2">
+        <v>21468</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1735</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="S29" s="1" t="s">
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="S29" s="2"/>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="2">
+        <v>21468</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>324</v>
+        <v>144</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>327</v>
+        <v>27</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>325</v>
+        <v>216</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>46</v>
+        <v>24</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1735</v>
       </c>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
@@ -7761,14 +7748,12 @@
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="2" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>96</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="S30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7848,10 +7833,10 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>105</v>
@@ -7893,10 +7878,10 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>105</v>
@@ -7938,10 +7923,10 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>105</v>
@@ -7983,10 +7968,10 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>105</v>
@@ -8028,16 +8013,16 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>42</v>
@@ -8046,7 +8031,7 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -8062,10 +8047,10 @@
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>96</v>
@@ -8073,16 +8058,16 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>105</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>42</v>
@@ -8091,7 +8076,7 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -8107,10 +8092,10 @@
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>96</v>
@@ -8118,10 +8103,10 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>76</v>
@@ -8136,7 +8121,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -8152,19 +8137,19 @@
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>76</v>
@@ -8179,7 +8164,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -8195,19 +8180,19 @@
       </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S9" s="2"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>76</v>
@@ -8222,7 +8207,7 @@
         <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -8241,16 +8226,16 @@
         <v>102</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S10" s="2"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>76</v>
@@ -8265,7 +8250,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -8284,16 +8269,16 @@
         <v>102</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S11" s="2"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>76</v>
@@ -8308,7 +8293,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -8327,16 +8312,16 @@
         <v>111</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S12" s="2"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>76</v>
@@ -8351,7 +8336,7 @@
         <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -8370,16 +8355,16 @@
         <v>111</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S13" s="2"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>76</v>
@@ -8394,7 +8379,7 @@
         <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -8413,16 +8398,16 @@
         <v>110</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S14" s="2"/>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>76</v>
@@ -8437,7 +8422,7 @@
         <v>21</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -8456,16 +8441,16 @@
         <v>110</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S15" s="2"/>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>76</v>
@@ -8480,7 +8465,7 @@
         <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -8499,16 +8484,16 @@
         <v>110</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S16" s="2"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>76</v>
@@ -8523,7 +8508,7 @@
         <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -8542,16 +8527,16 @@
         <v>110</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>76</v>
@@ -8566,7 +8551,7 @@
         <v>21</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -8585,16 +8570,16 @@
         <v>102</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S18" s="2"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>76</v>
@@ -8609,7 +8594,7 @@
         <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -8628,16 +8613,16 @@
         <v>102</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>76</v>
@@ -8652,7 +8637,7 @@
         <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -8677,10 +8662,10 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>76</v>
@@ -8695,7 +8680,7 @@
         <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -8720,10 +8705,10 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>76</v>
@@ -8738,7 +8723,7 @@
         <v>21</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -8754,19 +8739,19 @@
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R22" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S22" s="2"/>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>76</v>
@@ -8781,7 +8766,7 @@
         <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -8797,19 +8782,19 @@
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R23" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S23" s="2"/>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>96</v>
@@ -8824,7 +8809,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>24</v>
@@ -8847,16 +8832,16 @@
         <v>83</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S24" s="1"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>96</v>
@@ -8871,7 +8856,7 @@
         <v>49</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>44</v>
@@ -8894,16 +8879,16 @@
         <v>83</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S25" s="6"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>96</v>
@@ -8918,7 +8903,7 @@
         <v>49</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>44</v>
@@ -8941,16 +8926,16 @@
         <v>83</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S26" s="6"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>96</v>
@@ -8965,7 +8950,7 @@
         <v>49</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>44</v>
@@ -8988,16 +8973,16 @@
         <v>83</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S27" s="6"/>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="6" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>96</v>
@@ -9012,7 +8997,7 @@
         <v>49</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>44</v>
@@ -9035,22 +9020,22 @@
         <v>83</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>42</v>
@@ -9059,7 +9044,7 @@
         <v>43</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -9084,16 +9069,16 @@
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>42</v>
@@ -9102,7 +9087,7 @@
         <v>43</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -9127,10 +9112,10 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>96</v>
@@ -9145,7 +9130,7 @@
         <v>43</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>24</v>
@@ -9165,19 +9150,19 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R31" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="S31" s="1"/>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>96</v>
@@ -9192,7 +9177,7 @@
         <v>43</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>24</v>
@@ -9212,19 +9197,19 @@
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R32" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="S32" s="1"/>
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>96</v>
@@ -9239,7 +9224,7 @@
         <v>49</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>44</v>
@@ -9259,19 +9244,19 @@
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
       <c r="Q33" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R33" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R33" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S33" s="6"/>
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>96</v>
@@ -9286,7 +9271,7 @@
         <v>49</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>44</v>
@@ -9306,19 +9291,19 @@
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
       <c r="Q34" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R34" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R34" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S34" s="6"/>
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>96</v>
@@ -9333,7 +9318,7 @@
         <v>49</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>44</v>
@@ -9353,19 +9338,19 @@
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R35" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R35" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S35" s="6"/>
     </row>
     <row r="36" spans="1:19">
       <c r="A36" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>96</v>
@@ -9380,7 +9365,7 @@
         <v>49</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>44</v>
@@ -9400,19 +9385,19 @@
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R36" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R36" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S36" s="6"/>
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>96</v>
@@ -9427,7 +9412,7 @@
         <v>69</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -9439,25 +9424,25 @@
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="S37" s="4"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>20</v>
@@ -9466,7 +9451,7 @@
         <v>21</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -9482,25 +9467,25 @@
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R38" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S38" s="3"/>
     </row>
     <row r="39" spans="1:19">
       <c r="A39" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>20</v>
@@ -9509,7 +9494,7 @@
         <v>21</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -9525,25 +9510,25 @@
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R39" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S39" s="3"/>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>27</v>
@@ -9552,7 +9537,7 @@
         <v>21</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -9571,22 +9556,22 @@
         <v>71</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S40" s="3"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>27</v>
@@ -9595,7 +9580,7 @@
         <v>21</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -9614,22 +9599,22 @@
         <v>71</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S41" s="3"/>
     </row>
     <row r="42" spans="1:19">
       <c r="A42" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>20</v>
@@ -9638,7 +9623,7 @@
         <v>21</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -9657,22 +9642,22 @@
         <v>71</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S42" s="3"/>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>20</v>
@@ -9681,7 +9666,7 @@
         <v>21</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -9700,22 +9685,22 @@
         <v>71</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S43" s="3"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>20</v>
@@ -9724,7 +9709,7 @@
         <v>21</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -9740,25 +9725,25 @@
       </c>
       <c r="P44" s="2"/>
       <c r="Q44" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="R44" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="R44" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="S44" s="3"/>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>20</v>
@@ -9767,7 +9752,7 @@
         <v>21</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -9783,10 +9768,10 @@
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="R45" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="S45" s="3"/>
     </row>
@@ -9869,10 +9854,10 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>76</v>
@@ -9887,7 +9872,7 @@
         <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="2"/>
@@ -9903,19 +9888,19 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>76</v>
@@ -9930,7 +9915,7 @@
         <v>21</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="2"/>
@@ -9946,19 +9931,19 @@
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S3" s="2"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>76</v>
@@ -9973,7 +9958,7 @@
         <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="2"/>
@@ -9992,16 +9977,16 @@
         <v>102</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>76</v>
@@ -10016,7 +10001,7 @@
         <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="2"/>
@@ -10035,16 +10020,16 @@
         <v>102</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S5" s="2"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>76</v>
@@ -10059,7 +10044,7 @@
         <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="2"/>
@@ -10078,16 +10063,16 @@
         <v>111</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S6" s="2"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>76</v>
@@ -10102,7 +10087,7 @@
         <v>21</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="2"/>
@@ -10121,16 +10106,16 @@
         <v>111</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S7" s="2"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>76</v>
@@ -10145,7 +10130,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="2"/>
@@ -10164,16 +10149,16 @@
         <v>110</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S8" s="2"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>76</v>
@@ -10188,7 +10173,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="2"/>
@@ -10207,16 +10192,16 @@
         <v>110</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S9" s="2"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>76</v>
@@ -10231,7 +10216,7 @@
         <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="2"/>
@@ -10250,16 +10235,16 @@
         <v>110</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S10" s="2"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>76</v>
@@ -10274,7 +10259,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="2"/>
@@ -10293,16 +10278,16 @@
         <v>110</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S11" s="2"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>76</v>
@@ -10317,7 +10302,7 @@
         <v>21</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="2"/>
@@ -10336,16 +10321,16 @@
         <v>102</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S12" s="2"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>76</v>
@@ -10360,7 +10345,7 @@
         <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="2"/>
@@ -10379,16 +10364,16 @@
         <v>102</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S13" s="2"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>76</v>
@@ -10403,7 +10388,7 @@
         <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -10428,10 +10413,10 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>76</v>
@@ -10446,7 +10431,7 @@
         <v>21</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -10471,10 +10456,10 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>76</v>
@@ -10489,7 +10474,7 @@
         <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -10505,19 +10490,19 @@
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S16" s="2"/>
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>76</v>
@@ -10532,7 +10517,7 @@
         <v>21</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -10548,25 +10533,25 @@
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S17" s="2"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>20</v>
@@ -10575,7 +10560,7 @@
         <v>21</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -10591,25 +10576,25 @@
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R18" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S18" s="2"/>
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>20</v>
@@ -10618,7 +10603,7 @@
         <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -10634,25 +10619,25 @@
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="S19" s="2"/>
     </row>
     <row r="20" spans="1:19">
       <c r="A20" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>27</v>
@@ -10661,7 +10646,7 @@
         <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -10680,22 +10665,22 @@
         <v>71</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S20" s="2"/>
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>27</v>
@@ -10704,7 +10689,7 @@
         <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -10723,22 +10708,22 @@
         <v>71</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S21" s="2"/>
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>20</v>
@@ -10747,7 +10732,7 @@
         <v>21</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -10766,22 +10751,22 @@
         <v>71</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S22" s="2"/>
     </row>
     <row r="23" spans="1:19">
       <c r="A23" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>20</v>
@@ -10790,7 +10775,7 @@
         <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -10809,22 +10794,22 @@
         <v>71</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S23" s="2"/>
     </row>
     <row r="24" spans="1:19">
       <c r="A24" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>20</v>
@@ -10833,7 +10818,7 @@
         <v>21</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="2"/>
@@ -10849,25 +10834,25 @@
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="S24" s="2"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>20</v>
@@ -10876,7 +10861,7 @@
         <v>21</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="2"/>
@@ -10892,19 +10877,19 @@
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="S25" s="2"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>96</v>
@@ -10919,7 +10904,7 @@
         <v>43</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>24</v>
@@ -10939,19 +10924,19 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>96</v>
@@ -10966,7 +10951,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>24</v>
@@ -10986,19 +10971,19 @@
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R27" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>96</v>
@@ -11013,7 +10998,7 @@
         <v>49</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>44</v>
@@ -11033,19 +11018,19 @@
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
       <c r="Q28" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R28" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R28" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>96</v>
@@ -11060,7 +11045,7 @@
         <v>49</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>44</v>
@@ -11080,19 +11065,19 @@
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
       <c r="Q29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R29" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R29" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S29" s="6"/>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>96</v>
@@ -11107,7 +11092,7 @@
         <v>49</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>44</v>
@@ -11127,19 +11112,19 @@
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R30" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S30" s="6"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>96</v>
@@ -11154,7 +11139,7 @@
         <v>49</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>44</v>
@@ -11174,25 +11159,25 @@
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
       <c r="Q31" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="R31" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="R31" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19">
       <c r="A32" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>42</v>
@@ -11201,7 +11186,7 @@
         <v>43</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>24</v>
@@ -11230,16 +11215,16 @@
     </row>
     <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>42</v>
@@ -11248,7 +11233,7 @@
         <v>43</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>24</v>
@@ -11277,16 +11262,16 @@
     </row>
     <row r="34" spans="1:19">
       <c r="A34" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>42</v>
@@ -11295,7 +11280,7 @@
         <v>43</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>24</v>
@@ -11324,16 +11309,16 @@
     </row>
     <row r="35" spans="1:19">
       <c r="A35" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>48</v>
@@ -11342,7 +11327,7 @@
         <v>49</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>44</v>
@@ -11371,16 +11356,16 @@
     </row>
     <row r="36" spans="1:19">
       <c r="A36" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>51</v>
@@ -11389,7 +11374,7 @@
         <v>49</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>44</v>
@@ -11418,10 +11403,10 @@
     </row>
     <row r="37" spans="1:19">
       <c r="A37" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>96</v>
@@ -11436,7 +11421,7 @@
         <v>43</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>24</v>
@@ -11459,16 +11444,16 @@
         <v>83</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S37" s="1"/>
     </row>
     <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>96</v>
@@ -11483,7 +11468,7 @@
         <v>43</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>24</v>
@@ -11506,16 +11491,16 @@
         <v>83</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S38" s="1"/>
     </row>
     <row r="39" spans="1:19">
       <c r="A39" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>96</v>
@@ -11530,7 +11515,7 @@
         <v>49</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>44</v>
@@ -11553,16 +11538,16 @@
         <v>83</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S39" s="6"/>
     </row>
     <row r="40" spans="1:19">
       <c r="A40" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>96</v>
@@ -11577,7 +11562,7 @@
         <v>49</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>44</v>
@@ -11600,16 +11585,16 @@
         <v>83</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="S40" s="6"/>
     </row>
     <row r="41" spans="1:19">
       <c r="A41" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>96</v>
@@ -11624,7 +11609,7 @@
         <v>43</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>24</v>
@@ -11647,16 +11632,16 @@
         <v>84</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S41" s="1"/>
     </row>
     <row r="42" spans="1:19">
       <c r="A42" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>96</v>
@@ -11671,7 +11656,7 @@
         <v>43</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>24</v>
@@ -11694,16 +11679,16 @@
         <v>84</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:19">
       <c r="A43" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>96</v>
@@ -11718,7 +11703,7 @@
         <v>49</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>44</v>
@@ -11741,16 +11726,16 @@
         <v>84</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S43" s="6"/>
     </row>
     <row r="44" spans="1:19">
       <c r="A44" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>96</v>
@@ -11765,7 +11750,7 @@
         <v>49</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
@@ -11781,19 +11766,19 @@
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
       <c r="Q44" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="S44" s="6"/>
     </row>
     <row r="45" spans="1:19">
       <c r="A45" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>96</v>
@@ -11808,7 +11793,7 @@
         <v>49</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
@@ -11824,19 +11809,19 @@
       <c r="O45" s="6"/>
       <c r="P45" s="6"/>
       <c r="Q45" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="S45" s="6"/>
     </row>
     <row r="46" spans="1:19">
       <c r="A46" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>96</v>
@@ -11851,7 +11836,7 @@
         <v>49</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
@@ -11867,19 +11852,19 @@
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="S46" s="6"/>
     </row>
     <row r="47" spans="1:19">
       <c r="A47" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>96</v>
@@ -11894,7 +11879,7 @@
         <v>69</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="4"/>
@@ -11906,10 +11891,10 @@
       <c r="O47" s="4"/>
       <c r="P47" s="4"/>
       <c r="Q47" s="5" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="S47" s="4"/>
     </row>
@@ -11992,10 +11977,10 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>108</v>
@@ -12004,7 +11989,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>43</v>
@@ -12029,7 +12014,7 @@
         <v>110</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>96</v>
@@ -12037,10 +12022,10 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>108</v>
@@ -12049,7 +12034,7 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>43</v>
@@ -12074,7 +12059,7 @@
         <v>110</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>96</v>
@@ -12082,10 +12067,10 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>96</v>
@@ -12100,7 +12085,7 @@
         <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>24</v>
@@ -12123,16 +12108,16 @@
         <v>99</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>96</v>
@@ -12147,7 +12132,7 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>24</v>
@@ -12170,16 +12155,16 @@
         <v>99</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>96</v>
@@ -12194,7 +12179,7 @@
         <v>49</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>44</v>
@@ -12214,19 +12199,19 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>96</v>
@@ -12241,7 +12226,7 @@
         <v>49</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>44</v>
@@ -12261,19 +12246,19 @@
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>96</v>
@@ -12288,7 +12273,7 @@
         <v>49</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>44</v>
@@ -12308,19 +12293,19 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>96</v>
@@ -12335,7 +12320,7 @@
         <v>49</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>44</v>
@@ -12355,19 +12340,19 @@
       <c r="O9" s="6"/>
       <c r="P9" s="6"/>
       <c r="Q9" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="S9" s="6"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>96</v>
@@ -12382,7 +12367,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>24</v>
@@ -12402,19 +12387,19 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="6" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>96</v>
@@ -12429,7 +12414,7 @@
         <v>49</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>44</v>
@@ -12449,19 +12434,19 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="6" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>96</v>
@@ -12476,7 +12461,7 @@
         <v>49</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>44</v>
@@ -12496,19 +12481,19 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
       <c r="Q12" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R12" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>96</v>
@@ -12523,7 +12508,7 @@
         <v>49</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>44</v>
@@ -12543,19 +12528,19 @@
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
       <c r="Q13" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>96</v>
@@ -12570,7 +12555,7 @@
         <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>44</v>
@@ -12590,25 +12575,25 @@
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R14" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>42</v>
@@ -12617,7 +12602,7 @@
         <v>43</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>24</v>
@@ -12637,10 +12622,10 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="R15" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>96</v>
@@ -12648,16 +12633,16 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -12666,7 +12651,7 @@
         <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>24</v>
@@ -12686,10 +12671,10 @@
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>96</v>
@@ -12697,16 +12682,16 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>48</v>
@@ -12715,7 +12700,7 @@
         <v>49</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>44</v>
@@ -12735,25 +12720,25 @@
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="R17" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="6" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>76</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>51</v>
@@ -12762,7 +12747,7 @@
         <v>49</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>44</v>
@@ -12782,10 +12767,10 @@
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="R18" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="S18" s="6"/>
     </row>
@@ -12794,7 +12779,7 @@
         <v>21689</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>96</v>
@@ -12809,7 +12794,7 @@
         <v>49</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
@@ -12825,10 +12810,10 @@
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="S19" s="6"/>
     </row>
@@ -12837,7 +12822,7 @@
         <v>21689</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>96</v>
@@ -12852,7 +12837,7 @@
         <v>49</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -12868,10 +12853,10 @@
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="S20" s="6"/>
     </row>
@@ -12880,7 +12865,7 @@
         <v>21689</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>96</v>
@@ -12895,7 +12880,7 @@
         <v>49</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -12911,10 +12896,10 @@
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="S21" s="6"/>
     </row>
@@ -12923,7 +12908,7 @@
         <v>21690</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>96</v>
@@ -12938,7 +12923,7 @@
         <v>49</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
@@ -12954,10 +12939,10 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="S22" s="6"/>
     </row>
@@ -12966,7 +12951,7 @@
         <v>21690</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>96</v>
@@ -12981,7 +12966,7 @@
         <v>49</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -12997,10 +12982,10 @@
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
       <c r="Q23" s="6" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="S23" s="6"/>
     </row>
@@ -13009,7 +12994,7 @@
         <v>21690</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>96</v>
@@ -13024,7 +13009,7 @@
         <v>49</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
@@ -13040,25 +13025,25 @@
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
       <c r="Q24" s="6" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="S24" s="6"/>
     </row>
     <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>42</v>
@@ -13067,7 +13052,7 @@
         <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>24</v>
@@ -13087,25 +13072,25 @@
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19">
       <c r="A26" s="6" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>48</v>
@@ -13114,7 +13099,7 @@
         <v>49</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>44</v>
@@ -13134,25 +13119,25 @@
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="S26" s="6"/>
     </row>
     <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>42</v>
@@ -13161,7 +13146,7 @@
         <v>43</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>24</v>
@@ -13181,25 +13166,25 @@
       </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19">
       <c r="A28" s="6" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>96</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>48</v>
@@ -13208,7 +13193,7 @@
         <v>49</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>44</v>
@@ -13228,25 +13213,25 @@
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19">
       <c r="A29" s="5" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>68</v>
@@ -13255,7 +13240,7 @@
         <v>69</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -13267,10 +13252,10 @@
       <c r="O29" s="4"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="S29" s="4"/>
     </row>
@@ -13354,16 +13339,16 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>42</v>
@@ -13372,7 +13357,7 @@
         <v>43</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
@@ -13395,22 +13380,22 @@
         <v>84</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="6" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>48</v>
@@ -13419,7 +13404,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>44</v>
@@ -13442,22 +13427,22 @@
         <v>84</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="S3" s="6"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>42</v>
@@ -13466,7 +13451,7 @@
         <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -13482,25 +13467,25 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>42</v>
@@ -13509,7 +13494,7 @@
         <v>43</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -13528,22 +13513,22 @@
         <v>37</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>42</v>
@@ -13552,7 +13537,7 @@
         <v>43</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -13571,22 +13556,22 @@
         <v>37</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>42</v>
@@ -13595,7 +13580,7 @@
         <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -13611,25 +13596,25 @@
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>42</v>
@@ -13638,7 +13623,7 @@
         <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -13654,25 +13639,25 @@
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>42</v>
@@ -13681,7 +13666,7 @@
         <v>43</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -13697,25 +13682,25 @@
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>42</v>
@@ -13724,7 +13709,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -13740,25 +13725,25 @@
       </c>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>42</v>
@@ -13767,7 +13752,7 @@
         <v>43</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -13792,16 +13777,16 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>42</v>
@@ -13810,7 +13795,7 @@
         <v>43</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -13835,16 +13820,16 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>42</v>
@@ -13853,7 +13838,7 @@
         <v>43</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>24</v>
@@ -13873,25 +13858,25 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>48</v>
@@ -13900,7 +13885,7 @@
         <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>44</v>
@@ -13920,25 +13905,25 @@
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>48</v>
@@ -13947,7 +13932,7 @@
         <v>49</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>44</v>
@@ -13967,25 +13952,25 @@
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
       <c r="Q15" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>42</v>
@@ -13994,7 +13979,7 @@
         <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -14019,16 +14004,16 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>76</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>42</v>
@@ -14037,7 +14022,7 @@
         <v>43</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -14136,16 +14121,16 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="6" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>48</v>
@@ -14154,7 +14139,7 @@
         <v>49</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -14170,26 +14155,26 @@
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="6" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>48</v>
@@ -14198,7 +14183,7 @@
         <v>49</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -14214,26 +14199,26 @@
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="6" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>48</v>
@@ -14242,7 +14227,7 @@
         <v>49</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -14258,26 +14243,26 @@
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>48</v>
@@ -14286,7 +14271,7 @@
         <v>49</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
@@ -14302,26 +14287,26 @@
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="6" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>48</v>
@@ -14330,7 +14315,7 @@
         <v>49</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -14346,26 +14331,26 @@
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>51</v>
@@ -14374,7 +14359,7 @@
         <v>49</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
@@ -14390,26 +14375,26 @@
       <c r="O7" s="6"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="6" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="S7" s="6"/>
       <c r="T7" s="6"/>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>51</v>
@@ -14418,7 +14403,7 @@
         <v>49</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -14434,10 +14419,10 @@
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
